--- a/Сценарий 4.xlsx
+++ b/Сценарий 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\macros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B81AE2-C5A7-4D04-BA59-19221A72836D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDFFBFD-1B4D-4F81-90E1-C60DB720D2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3232,19 +3232,19 @@
         <v>71</v>
       </c>
       <c r="AM8" s="36">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="36">
-        <v>158.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="36">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="36">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AQ8" s="36">
-        <v>205</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8063,11 +8063,11 @@
     <row r="74" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L74" s="27">
         <f>L84*0.973</f>
-        <v>126.49</v>
-      </c>
-      <c r="M74" s="79">
+        <v>0</v>
+      </c>
+      <c r="M74" s="79" t="e">
         <f>L74/$L$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="29">
         <v>0</v>
@@ -8078,11 +8078,11 @@
       </c>
       <c r="Q74" s="27">
         <f>Q84*0.973</f>
-        <v>153.92859999999999</v>
-      </c>
-      <c r="R74" s="79">
+        <v>0</v>
+      </c>
+      <c r="R74" s="79" t="e">
         <f>Q74/$Q$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S74" s="29">
         <v>0</v>
@@ -8093,11 +8093,11 @@
       </c>
       <c r="V74" s="27">
         <f>V84*0.973</f>
-        <v>194.6</v>
-      </c>
-      <c r="W74" s="79">
+        <v>0</v>
+      </c>
+      <c r="W74" s="79" t="e">
         <f>V74/$V$74</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X74" s="29">
         <v>0</v>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="AA74" s="27">
         <f>AA84*0.973</f>
-        <v>197.90819999999999</v>
+        <v>39.348119999999994</v>
       </c>
       <c r="AB74" s="79">
         <f>AA74/$AA$74</f>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="AF74" s="27">
         <f>AA84</f>
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AG74" s="28">
         <f t="shared" ref="AG74:AG84" si="80">AF74/$AF$74</f>
@@ -8140,11 +8140,11 @@
     <row r="75" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L75" s="31">
         <f t="shared" ref="L75:L83" si="82">L74+(L$84-L$74)/10</f>
-        <v>126.84099999999999</v>
-      </c>
-      <c r="M75" s="79">
+        <v>0</v>
+      </c>
+      <c r="M75" s="79" t="e">
         <f t="shared" ref="M75:M84" si="83">L75/$L$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="33">
         <v>0.1</v>
@@ -8155,11 +8155,11 @@
       </c>
       <c r="Q75" s="31">
         <f t="shared" ref="Q75:Q83" si="84">Q74+(Q$84-Q$74)/10</f>
-        <v>154.35574</v>
-      </c>
-      <c r="R75" s="79">
+        <v>0</v>
+      </c>
+      <c r="R75" s="79" t="e">
         <f t="shared" ref="R75:R84" si="85">Q75/$Q$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S75" s="33">
         <v>0.1</v>
@@ -8170,11 +8170,11 @@
       </c>
       <c r="V75" s="31">
         <f t="shared" ref="V75:V83" si="86">V74+(V$84-V$74)/10</f>
-        <v>195.14</v>
-      </c>
-      <c r="W75" s="79">
+        <v>0</v>
+      </c>
+      <c r="W75" s="79" t="e">
         <f t="shared" ref="W75:W84" si="87">V75/$V$74</f>
-        <v>1.0027749229188079</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X75" s="33">
         <v>0.1</v>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="AA75" s="31">
         <f t="shared" ref="AA75:AA83" si="88">AA74+(AA$84-AA$74)/10</f>
-        <v>198.45738</v>
+        <v>39.457307999999998</v>
       </c>
       <c r="AB75" s="79">
         <f t="shared" ref="AB75:AB84" si="89">AA75/$AA$74</f>
@@ -8200,11 +8200,11 @@
       </c>
       <c r="AF75" s="31">
         <f t="shared" ref="AF75:AF83" si="90">AF74+(AF$84-AF$74)/10</f>
-        <v>203.56</v>
+        <v>40.574999999999996</v>
       </c>
       <c r="AG75" s="32">
         <f t="shared" si="80"/>
-        <v>1.0007866273352999</v>
+        <v>1.0033382789317506</v>
       </c>
       <c r="AH75" s="33">
         <v>0.1</v>
@@ -8217,11 +8217,11 @@
     <row r="76" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L76" s="31">
         <f t="shared" si="82"/>
-        <v>127.19199999999999</v>
-      </c>
-      <c r="M76" s="79">
+        <v>0</v>
+      </c>
+      <c r="M76" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0055498458376155</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="33">
         <v>0.2</v>
@@ -8232,11 +8232,11 @@
       </c>
       <c r="Q76" s="31">
         <f t="shared" si="84"/>
-        <v>154.78288000000001</v>
-      </c>
-      <c r="R76" s="79">
+        <v>0</v>
+      </c>
+      <c r="R76" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0055498458376158</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S76" s="33">
         <v>0.2</v>
@@ -8247,11 +8247,11 @@
       </c>
       <c r="V76" s="31">
         <f t="shared" si="86"/>
-        <v>195.67999999999998</v>
-      </c>
-      <c r="W76" s="79">
+        <v>0</v>
+      </c>
+      <c r="W76" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0055498458376155</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X76" s="33">
         <v>0.2</v>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AA76" s="31">
         <f t="shared" si="88"/>
-        <v>199.00656000000001</v>
+        <v>39.566496000000001</v>
       </c>
       <c r="AB76" s="79">
         <f t="shared" si="89"/>
@@ -8277,11 +8277,11 @@
       </c>
       <c r="AF76" s="31">
         <f t="shared" si="90"/>
-        <v>203.72</v>
+        <v>40.709999999999994</v>
       </c>
       <c r="AG76" s="32">
         <f t="shared" si="80"/>
-        <v>1.0015732546705998</v>
+        <v>1.0066765578635013</v>
       </c>
       <c r="AH76" s="33">
         <v>0.2</v>
@@ -8294,11 +8294,11 @@
     <row r="77" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L77" s="31">
         <f t="shared" si="82"/>
-        <v>127.54299999999999</v>
-      </c>
-      <c r="M77" s="79">
+        <v>0</v>
+      </c>
+      <c r="M77" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0083247687564234</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="33">
         <v>0.3</v>
@@ -8309,11 +8309,11 @@
       </c>
       <c r="Q77" s="31">
         <f t="shared" si="84"/>
-        <v>155.21002000000001</v>
-      </c>
-      <c r="R77" s="79">
+        <v>0</v>
+      </c>
+      <c r="R77" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0083247687564236</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S77" s="33">
         <v>0.3</v>
@@ -8324,11 +8324,11 @@
       </c>
       <c r="V77" s="31">
         <f t="shared" si="86"/>
-        <v>196.21999999999997</v>
-      </c>
-      <c r="W77" s="79">
+        <v>0</v>
+      </c>
+      <c r="W77" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0083247687564234</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X77" s="33">
         <v>0.3</v>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AA77" s="31">
         <f t="shared" si="88"/>
-        <v>199.55574000000001</v>
+        <v>39.675684000000004</v>
       </c>
       <c r="AB77" s="79">
         <f t="shared" si="89"/>
@@ -8354,11 +8354,11 @@
       </c>
       <c r="AF77" s="31">
         <f t="shared" si="90"/>
-        <v>203.88</v>
+        <v>40.844999999999992</v>
       </c>
       <c r="AG77" s="32">
         <f t="shared" si="80"/>
-        <v>1.0023598820058996</v>
+        <v>1.0100148367952522</v>
       </c>
       <c r="AH77" s="33">
         <v>0.3</v>
@@ -8371,11 +8371,11 @@
     <row r="78" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L78" s="31">
         <f t="shared" si="82"/>
-        <v>127.89399999999999</v>
-      </c>
-      <c r="M78" s="79">
+        <v>0</v>
+      </c>
+      <c r="M78" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0110996916752313</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="33">
         <v>0.4</v>
@@ -8386,11 +8386,11 @@
       </c>
       <c r="Q78" s="31">
         <f t="shared" si="84"/>
-        <v>155.63716000000002</v>
-      </c>
-      <c r="R78" s="79">
+        <v>0</v>
+      </c>
+      <c r="R78" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0110996916752315</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S78" s="33">
         <v>0.4</v>
@@ -8401,11 +8401,11 @@
       </c>
       <c r="V78" s="31">
         <f t="shared" si="86"/>
-        <v>196.75999999999996</v>
-      </c>
-      <c r="W78" s="79">
+        <v>0</v>
+      </c>
+      <c r="W78" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0110996916752311</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X78" s="33">
         <v>0.4</v>
@@ -8416,11 +8416,11 @@
       </c>
       <c r="AA78" s="31">
         <f t="shared" si="88"/>
-        <v>200.10492000000002</v>
+        <v>39.784872000000007</v>
       </c>
       <c r="AB78" s="79">
         <f t="shared" si="89"/>
-        <v>1.0110996916752313</v>
+        <v>1.0110996916752315</v>
       </c>
       <c r="AC78" s="33">
         <v>0.4</v>
@@ -8431,11 +8431,11 @@
       </c>
       <c r="AF78" s="31">
         <f t="shared" si="90"/>
-        <v>204.04</v>
+        <v>40.97999999999999</v>
       </c>
       <c r="AG78" s="32">
         <f t="shared" si="80"/>
-        <v>1.0031465093411995</v>
+        <v>1.0133531157270028</v>
       </c>
       <c r="AH78" s="33">
         <v>0.4</v>
@@ -8448,11 +8448,11 @@
     <row r="79" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L79" s="31">
         <f t="shared" si="82"/>
-        <v>128.245</v>
-      </c>
-      <c r="M79" s="79">
+        <v>0</v>
+      </c>
+      <c r="M79" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0138746145940392</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="33">
         <v>0.5</v>
@@ -8463,11 +8463,11 @@
       </c>
       <c r="Q79" s="31">
         <f t="shared" si="84"/>
-        <v>156.06430000000003</v>
-      </c>
-      <c r="R79" s="79">
+        <v>0</v>
+      </c>
+      <c r="R79" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0138746145940394</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S79" s="33">
         <v>0.5</v>
@@ -8478,11 +8478,11 @@
       </c>
       <c r="V79" s="31">
         <f t="shared" si="86"/>
-        <v>197.29999999999995</v>
-      </c>
-      <c r="W79" s="79">
+        <v>0</v>
+      </c>
+      <c r="W79" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0138746145940389</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X79" s="33">
         <v>0.5</v>
@@ -8493,11 +8493,11 @@
       </c>
       <c r="AA79" s="31">
         <f t="shared" si="88"/>
-        <v>200.65410000000003</v>
+        <v>39.89406000000001</v>
       </c>
       <c r="AB79" s="79">
         <f t="shared" si="89"/>
-        <v>1.0138746145940392</v>
+        <v>1.0138746145940394</v>
       </c>
       <c r="AC79" s="33">
         <v>0.5</v>
@@ -8508,11 +8508,11 @@
       </c>
       <c r="AF79" s="31">
         <f t="shared" si="90"/>
-        <v>204.2</v>
+        <v>41.114999999999988</v>
       </c>
       <c r="AG79" s="32">
         <f t="shared" si="80"/>
-        <v>1.0039331366764994</v>
+        <v>1.0166913946587535</v>
       </c>
       <c r="AH79" s="33">
         <v>0.5</v>
@@ -8525,11 +8525,11 @@
     <row r="80" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L80" s="31">
         <f t="shared" si="82"/>
-        <v>128.596</v>
-      </c>
-      <c r="M80" s="79">
+        <v>0</v>
+      </c>
+      <c r="M80" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.016649537512847</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="33">
         <v>0.6</v>
@@ -8540,11 +8540,11 @@
       </c>
       <c r="Q80" s="31">
         <f t="shared" si="84"/>
-        <v>156.49144000000004</v>
-      </c>
-      <c r="R80" s="79">
+        <v>0</v>
+      </c>
+      <c r="R80" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0166495375128473</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S80" s="33">
         <v>0.6</v>
@@ -8555,11 +8555,11 @@
       </c>
       <c r="V80" s="31">
         <f t="shared" si="86"/>
-        <v>197.83999999999995</v>
-      </c>
-      <c r="W80" s="79">
+        <v>0</v>
+      </c>
+      <c r="W80" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0166495375128466</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X80" s="33">
         <v>0.6</v>
@@ -8570,11 +8570,11 @@
       </c>
       <c r="AA80" s="31">
         <f t="shared" si="88"/>
-        <v>201.20328000000003</v>
+        <v>40.003248000000013</v>
       </c>
       <c r="AB80" s="79">
         <f t="shared" si="89"/>
-        <v>1.016649537512847</v>
+        <v>1.0166495375128473</v>
       </c>
       <c r="AC80" s="33">
         <v>0.6</v>
@@ -8585,11 +8585,11 @@
       </c>
       <c r="AF80" s="31">
         <f t="shared" si="90"/>
-        <v>204.35999999999999</v>
+        <v>41.249999999999986</v>
       </c>
       <c r="AG80" s="32">
         <f t="shared" si="80"/>
-        <v>1.0047197640117993</v>
+        <v>1.0200296735905041</v>
       </c>
       <c r="AH80" s="33">
         <v>0.6</v>
@@ -8602,11 +8602,11 @@
     <row r="81" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L81" s="31">
         <f t="shared" si="82"/>
-        <v>128.947</v>
-      </c>
-      <c r="M81" s="79">
+        <v>0</v>
+      </c>
+      <c r="M81" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0194244604316547</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N81" s="33">
         <v>0.7</v>
@@ -8617,11 +8617,11 @@
       </c>
       <c r="Q81" s="31">
         <f t="shared" si="84"/>
-        <v>156.91858000000005</v>
-      </c>
-      <c r="R81" s="79">
+        <v>0</v>
+      </c>
+      <c r="R81" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0194244604316551</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S81" s="33">
         <v>0.7</v>
@@ -8632,11 +8632,11 @@
       </c>
       <c r="V81" s="31">
         <f t="shared" si="86"/>
-        <v>198.37999999999994</v>
-      </c>
-      <c r="W81" s="79">
+        <v>0</v>
+      </c>
+      <c r="W81" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0194244604316545</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X81" s="33">
         <v>0.7</v>
@@ -8647,11 +8647,11 @@
       </c>
       <c r="AA81" s="31">
         <f t="shared" si="88"/>
-        <v>201.75246000000004</v>
+        <v>40.112436000000017</v>
       </c>
       <c r="AB81" s="79">
         <f t="shared" si="89"/>
-        <v>1.0194244604316549</v>
+        <v>1.0194244604316551</v>
       </c>
       <c r="AC81" s="33">
         <v>0.7</v>
@@ -8662,11 +8662,11 @@
       </c>
       <c r="AF81" s="31">
         <f t="shared" si="90"/>
-        <v>204.51999999999998</v>
+        <v>41.384999999999984</v>
       </c>
       <c r="AG81" s="32">
         <f t="shared" si="80"/>
-        <v>1.0055063913470992</v>
+        <v>1.0233679525222548</v>
       </c>
       <c r="AH81" s="33">
         <v>0.7</v>
@@ -8679,11 +8679,11 @@
     <row r="82" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L82" s="31">
         <f t="shared" si="82"/>
-        <v>129.298</v>
-      </c>
-      <c r="M82" s="79">
+        <v>0</v>
+      </c>
+      <c r="M82" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0221993833504626</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N82" s="33">
         <v>0.8</v>
@@ -8694,11 +8694,11 @@
       </c>
       <c r="Q82" s="31">
         <f t="shared" si="84"/>
-        <v>157.34572000000006</v>
-      </c>
-      <c r="R82" s="79">
+        <v>0</v>
+      </c>
+      <c r="R82" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.022199383350463</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S82" s="33">
         <v>0.8</v>
@@ -8709,11 +8709,11 @@
       </c>
       <c r="V82" s="31">
         <f t="shared" si="86"/>
-        <v>198.91999999999993</v>
-      </c>
-      <c r="W82" s="79">
+        <v>0</v>
+      </c>
+      <c r="W82" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0221993833504621</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X82" s="33">
         <v>0.8</v>
@@ -8724,11 +8724,11 @@
       </c>
       <c r="AA82" s="31">
         <f t="shared" si="88"/>
-        <v>202.30164000000005</v>
+        <v>40.22162400000002</v>
       </c>
       <c r="AB82" s="79">
         <f t="shared" si="89"/>
-        <v>1.0221993833504628</v>
+        <v>1.0221993833504632</v>
       </c>
       <c r="AC82" s="33">
         <v>0.8</v>
@@ -8739,11 +8739,11 @@
       </c>
       <c r="AF82" s="31">
         <f t="shared" si="90"/>
-        <v>204.67999999999998</v>
+        <v>41.519999999999982</v>
       </c>
       <c r="AG82" s="32">
         <f t="shared" si="80"/>
-        <v>1.0062930186823991</v>
+        <v>1.0267062314540056</v>
       </c>
       <c r="AH82" s="33">
         <v>0.8</v>
@@ -8756,11 +8756,11 @@
     <row r="83" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L83" s="31">
         <f t="shared" si="82"/>
-        <v>129.649</v>
-      </c>
-      <c r="M83" s="79">
+        <v>0</v>
+      </c>
+      <c r="M83" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0249743062692704</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N83" s="33">
         <v>0.9</v>
@@ -8771,11 +8771,11 @@
       </c>
       <c r="Q83" s="31">
         <f t="shared" si="84"/>
-        <v>157.77286000000007</v>
-      </c>
-      <c r="R83" s="79">
+        <v>0</v>
+      </c>
+      <c r="R83" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0249743062692709</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S83" s="33">
         <v>0.9</v>
@@ -8786,11 +8786,11 @@
       </c>
       <c r="V83" s="31">
         <f t="shared" si="86"/>
-        <v>199.45999999999992</v>
-      </c>
-      <c r="W83" s="79">
+        <v>0</v>
+      </c>
+      <c r="W83" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.02497430626927</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X83" s="33">
         <v>0.9</v>
@@ -8801,11 +8801,11 @@
       </c>
       <c r="AA83" s="31">
         <f t="shared" si="88"/>
-        <v>202.85082000000006</v>
+        <v>40.330812000000023</v>
       </c>
       <c r="AB83" s="79">
         <f t="shared" si="89"/>
-        <v>1.0249743062692707</v>
+        <v>1.0249743062692711</v>
       </c>
       <c r="AC83" s="33">
         <v>0.9</v>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="AF83" s="31">
         <f t="shared" si="90"/>
-        <v>204.83999999999997</v>
+        <v>41.65499999999998</v>
       </c>
       <c r="AG83" s="32">
         <f t="shared" si="80"/>
-        <v>1.0070796460176989</v>
+        <v>1.0300445103857563</v>
       </c>
       <c r="AH83" s="33">
         <v>0.9</v>
@@ -8833,11 +8833,11 @@
     <row r="84" spans="12:35" x14ac:dyDescent="0.25">
       <c r="L84" s="78">
         <f>$AM$8</f>
-        <v>130</v>
-      </c>
-      <c r="M84" s="79">
+        <v>0</v>
+      </c>
+      <c r="M84" s="79" t="e">
         <f t="shared" si="83"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N84" s="41">
         <v>1</v>
@@ -8848,11 +8848,11 @@
       </c>
       <c r="Q84" s="78">
         <f>$AN$8</f>
-        <v>158.19999999999999</v>
-      </c>
-      <c r="R84" s="79">
+        <v>0</v>
+      </c>
+      <c r="R84" s="79" t="e">
         <f t="shared" si="85"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S84" s="41">
         <v>1</v>
@@ -8863,11 +8863,11 @@
       </c>
       <c r="V84" s="78">
         <f>$AO$8</f>
-        <v>200</v>
-      </c>
-      <c r="W84" s="79">
+        <v>0</v>
+      </c>
+      <c r="W84" s="79" t="e">
         <f t="shared" si="87"/>
-        <v>1.0277492291880781</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="X84" s="41">
         <v>1</v>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AA84" s="78">
         <f>$AP$8</f>
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AB84" s="79">
         <f t="shared" si="89"/>
@@ -8893,11 +8893,11 @@
       </c>
       <c r="AF84" s="78">
         <f>$AQ$8</f>
-        <v>205</v>
+        <v>41.79</v>
       </c>
       <c r="AG84" s="81">
         <f t="shared" si="80"/>
-        <v>1.0078662733529991</v>
+        <v>1.0333827893175074</v>
       </c>
       <c r="AH84" s="41">
         <v>1</v>
